--- a/artfynd/A 1481-2022 artfynd.xlsx
+++ b/artfynd/A 1481-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1481-2022 artfynd.xlsx
+++ b/artfynd/A 1481-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>73542711</v>
       </c>
       <c r="B2" t="n">
-        <v>81626</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83687</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>378882.8494907903</v>
+        <v>378883</v>
       </c>
       <c r="R2" t="n">
-        <v>6182059.518898268</v>
+        <v>6182060</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,19 +753,9 @@
           <t>2018-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -801,65 +786,61 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catharina  Nilsson </t>
+          <t>Catharina  Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catharina  Nilsson </t>
+          <t>Catharina  Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80666606</v>
+        <v>97758008</v>
       </c>
       <c r="B3" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>4191</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tallplanteringar vid gamla cementgjuteriet, Sk</t>
+          <t>Skytteskogsvägen, Kävlinge, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>378960.924659308</v>
+        <v>378950</v>
       </c>
       <c r="R3" t="n">
-        <v>6182190.142744064</v>
+        <v>6182175</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,22 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,27 +884,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Nellie Linander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Nellie Linander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97758008</v>
+        <v>107931501</v>
       </c>
       <c r="B4" t="n">
-        <v>88852</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,35 +907,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4191</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skytteskogsvägen, Kävlinge, Sk</t>
+          <t>Skytteskogsvägen 33, Kävlinge, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>378950.359472178</v>
+        <v>378892</v>
       </c>
       <c r="R4" t="n">
-        <v>6182175.244116287</v>
+        <v>6182260</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +999,442 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Mikael Arinder</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Arinder</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>93490856</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8855</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100260</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kardinalrödrock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ampedus cardinalis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schiödte, 1865)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Harmonikevägen 7, Furulund, Kävlinge., Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>379019</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6182013</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kävlinge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stävie</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-05-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-05-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Göran Brandin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Göran Brandin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>80666606</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tallplanteringar vid gamla cementgjuteriet, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>378961</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6182190</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kävlinge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stävie</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-06-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-06-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emil Åsegård</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil Åsegård</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>107931505</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skytteskogsvägen 33, Kävlinge, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>378892</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6182260</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kävlinge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stävie</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-04-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-04-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Arinder</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Arinder</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97071464</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lundåker, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>378797</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6181984</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kävlinge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stävie</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-10-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Nellie Linander</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Nellie Linander</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1481-2022 artfynd.xlsx
+++ b/artfynd/A 1481-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97071464</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73542711</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97758008</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107931501</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93490856</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80666606</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,8 +1470,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107931505</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>